--- a/LLM/usecases.xlsx
+++ b/LLM/usecases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgrammingProjects\PyProjects\LLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1DE94E-9353-4E06-A5F6-D43CA0DBB816}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C954892-B98A-458A-8BE9-60CBA6F487BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/LLM/usecases.xlsx
+++ b/LLM/usecases.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgrammingProjects\UsUcLLMs\LLM\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA255B28-6361-4C88-BDB2-77601D2B46DD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7521D141-24B3-4590-B779-D742055F4038}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="35" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LLMs" sheetId="1" r:id="rId1"/>
@@ -6292,6 +6287,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF008000"/>
+      <color rgb="FF0000CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -6317,37 +6318,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -6370,7 +6341,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="0000CC"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6453,7 +6424,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="008000"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6536,7 +6507,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6611,8 +6582,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
         <c:axId val="528240976"/>
         <c:axId val="523296032"/>
       </c:barChart>
@@ -6623,6 +6594,61 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Dataset</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -6672,53 +6698,67 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Inter-LLM Agreement</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:majorGridlines>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="528240976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -6732,7 +6772,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9977,6 +10017,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10080,6 +10121,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12414,6 +12456,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12517,6 +12560,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13235,6 +13279,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14533,6 +14578,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15209,6 +15255,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16439,6 +16486,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -17477,6 +17525,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19353,6 +19402,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -21352,6 +21402,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -22439,6 +22490,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24400,6 +24452,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24983,6 +25036,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -26043,6 +26097,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -26795,6 +26850,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28161,6 +28217,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28645,6 +28702,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28754,6 +28812,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29294,6 +29353,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29403,6 +29463,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29506,6 +29567,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30032,6 +30094,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30141,6 +30204,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30544,6 +30608,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30653,6 +30718,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31067,6 +31133,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31176,6 +31243,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31589,6 +31657,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31698,6 +31767,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34639,6 +34709,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34742,6 +34813,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -36886,6 +36958,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -36989,6 +37062,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -39059,6 +39133,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -39162,5 +39237,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>